--- a/i_test/05_02_test_DANREG_hierarchy/i_input_xls/groups_of_pregnancies.xlsx
+++ b/i_test/05_02_test_DANREG_hierarchy/i_input_xls/groups_of_pregnancies.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giorg\GitHub\ConcePTIONAlgorithmPregnancies\i_test\05_02_test_VID_maxgap_70\i_input_xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\Unipi-Unifi\ConcePTIONAlgorithmPregnancies\i_test\05_02_test_DANREG_hierarchy\i_input_xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862C52AE-900F-424D-9808-46F296544577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA6A861-F6E4-4AF6-9113-4C3D1BFAB4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30195" yWindow="1395" windowWidth="25110" windowHeight="13500" xr2:uid="{D3BF36C2-B984-433A-919C-623886B267BE}"/>
+    <workbookView xWindow="-28920" yWindow="525" windowWidth="29040" windowHeight="15720" xr2:uid="{D3BF36C2-B984-433A-919C-623886B267BE}"/>
   </bookViews>
   <sheets>
     <sheet name="groups_of_pregnancies" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="50">
   <si>
     <t>pregnancy_id</t>
   </si>
@@ -109,145 +109,70 @@
     <t>ID</t>
   </si>
   <si>
-    <t>ConCDM_SIM_200421_00025_SDO_45_2007-01-05</t>
-  </si>
-  <si>
     <t>ConCDM_SIM_200421_00025</t>
   </si>
   <si>
-    <t>UNK</t>
-  </si>
-  <si>
     <t>ICD9</t>
   </si>
   <si>
     <t>SDO</t>
   </si>
   <si>
-    <t>hospitalisation_secondary</t>
-  </si>
-  <si>
-    <t>SDO_45</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
     <t>yes</t>
   </si>
   <si>
-    <t>4_red</t>
-  </si>
-  <si>
     <t>ConCDM_SIM_200421_00025_SDO_44_2003-06-13</t>
   </si>
   <si>
-    <t>imputed_from_BirthNarrowLB</t>
-  </si>
-  <si>
-    <t>from_BirthNarrowLB</t>
-  </si>
-  <si>
-    <t>LB</t>
-  </si>
-  <si>
     <t>SDO_44</t>
   </si>
   <si>
-    <t>BirthNarrowLB</t>
-  </si>
-  <si>
     <t>2_yellow</t>
   </si>
   <si>
-    <t>V272</t>
-  </si>
-  <si>
-    <t>ConCDM_SIM_200421_00025_SDO_45_2007-01-05_2</t>
-  </si>
-  <si>
     <t>imputed_from_BirthNarrowBUNSP</t>
   </si>
   <si>
     <t>from_BirthNarrowBUNSP</t>
   </si>
   <si>
-    <t>UNSP</t>
-  </si>
-  <si>
-    <t>hospitalisation_primary</t>
-  </si>
-  <si>
-    <t>BirthNarrowBUNSP</t>
-  </si>
-  <si>
     <t>ConCDM_SIM_200421_00025_SDO_44_2003-06-13_2</t>
   </si>
   <si>
-    <t>ConCDM_SIM_200421_00025_SDO_45_2007-01-05_3</t>
-  </si>
-  <si>
-    <t>imputed_from_Birth_possible</t>
-  </si>
-  <si>
-    <t>Birth_possible</t>
-  </si>
-  <si>
-    <t>ConCDM_SIM_200421_00025_SDO_45_2007-01-05_4</t>
-  </si>
-  <si>
     <t>ConCDM_SIM_200421_00025_SDO_44_2003-06-04</t>
   </si>
   <si>
     <t>imputed_from_procedures_end_UNK</t>
   </si>
   <si>
-    <t>procedure_during_hospitalisation</t>
-  </si>
-  <si>
-    <t>procedures_end_UNK</t>
-  </si>
-  <si>
     <t>ConCDM_SIM_200421_00025_SDO_44_2003-06-04_1</t>
   </si>
   <si>
-    <t>ConCDM_SIM_200421_00025_SDO_41_2009-07-13</t>
-  </si>
-  <si>
-    <t>imputed_from_Interruption_narrow</t>
-  </si>
-  <si>
-    <t>SDO_41</t>
-  </si>
-  <si>
-    <t>ConCDM_SIM_200421_00025_SDO_41_2009-07-13_1</t>
-  </si>
-  <si>
-    <t>ConCDM_SIM_200421_00025_SDO_41_2009-07-29</t>
-  </si>
-  <si>
-    <t>imputed_from_procedures_termination</t>
-  </si>
-  <si>
-    <t>ConCDM_SIM_200421_00025_SDO_41_2009-07-29_1</t>
-  </si>
-  <si>
     <t>SB</t>
   </si>
   <si>
-    <t>from_StillBirth_narrow</t>
-  </si>
-  <si>
-    <t>StillBirth_narrow</t>
-  </si>
-  <si>
-    <t>imputed</t>
-  </si>
-  <si>
-    <t>from_</t>
-  </si>
-  <si>
-    <t>imputed_</t>
+    <t>emergency_hospital_contact_primary</t>
+  </si>
+  <si>
+    <t>meaning_secondary</t>
+  </si>
+  <si>
+    <t>stillbirth_narrow</t>
+  </si>
+  <si>
+    <t>ConCDM_SIM_200421_00026</t>
+  </si>
+  <si>
+    <t>ConCDM_SIM_200421_00026_SDO_45_2007-01-05</t>
+  </si>
+  <si>
+    <t>ConCDM_SIM_200421_00026_SDO_44_2003-06-04_1</t>
+  </si>
+  <si>
+    <t>ConCDM_SIM_200421_00026_SDO_44_2003-06-13_2</t>
   </si>
 </sst>
 </file>
@@ -737,11 +662,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Colore 1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1117,21 +1041,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2D1FFE-C4F6-44C3-9429-6E36118E76E6}">
-  <dimension ref="A1:AB11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AB5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.88671875" customWidth="1"/>
+    <col min="1" max="1" width="48.90625" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" customWidth="1"/>
-    <col min="9" max="9" width="32.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="26.109375" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" customWidth="1"/>
+    <col min="9" max="9" width="32.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="26.08984375" customWidth="1"/>
+    <col min="28" max="28" width="44.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1217,12 +1143,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1">
         <v>37776</v>
@@ -1231,16 +1157,16 @@
         <v>37496</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="H2" s="1">
         <v>37776</v>
       </c>
       <c r="I2" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="J2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="K2">
         <v>741</v>
@@ -1252,45 +1178,45 @@
         <v>0</v>
       </c>
       <c r="O2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T2" t="s">
+        <v>31</v>
+      </c>
+      <c r="U2" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" t="s">
         <v>32</v>
       </c>
-      <c r="P2" t="s">
-        <v>59</v>
-      </c>
-      <c r="S2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="W2" t="s">
+        <v>45</v>
+      </c>
+      <c r="X2" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z2" t="s">
         <v>35</v>
       </c>
-      <c r="U2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W2" t="s">
-        <v>60</v>
-      </c>
-      <c r="X2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>44</v>
-      </c>
       <c r="AA2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AB2" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="1">
         <v>37785</v>
@@ -1299,22 +1225,22 @@
         <v>37505</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="H3" s="1">
         <v>37785</v>
       </c>
       <c r="I3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="J3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="K3">
         <v>65801</v>
       </c>
       <c r="L3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -1323,603 +1249,176 @@
         <v>0</v>
       </c>
       <c r="O3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" t="s">
+        <v>44</v>
+      </c>
+      <c r="S3" t="s">
+        <v>34</v>
+      </c>
+      <c r="T3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V3" t="s">
         <v>32</v>
       </c>
-      <c r="P3" t="s">
-        <v>50</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA3">
+        <v>20.5</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="1">
+        <v>37776</v>
+      </c>
+      <c r="D4" s="1">
+        <v>37496</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="1">
+        <v>37776</v>
+      </c>
+      <c r="I4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J4" t="s">
         <v>42</v>
       </c>
-      <c r="T3" t="s">
+      <c r="K4">
+        <v>741</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" t="s">
+        <v>34</v>
+      </c>
+      <c r="T4" t="s">
+        <v>31</v>
+      </c>
+      <c r="U4" t="s">
+        <v>31</v>
+      </c>
+      <c r="V4" t="s">
+        <v>32</v>
+      </c>
+      <c r="W4" t="s">
+        <v>45</v>
+      </c>
+      <c r="X4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z4" t="s">
         <v>35</v>
       </c>
-      <c r="U3" t="s">
+      <c r="AA4">
+        <v>10</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="1">
+        <v>37785</v>
+      </c>
+      <c r="D5" s="1">
+        <v>37505</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="1">
+        <v>37785</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5">
+        <v>65801</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>30</v>
+      </c>
+      <c r="P5" t="s">
+        <v>44</v>
+      </c>
+      <c r="S5" t="s">
+        <v>34</v>
+      </c>
+      <c r="T5" t="s">
+        <v>31</v>
+      </c>
+      <c r="U5" t="s">
+        <v>31</v>
+      </c>
+      <c r="V5" t="s">
+        <v>32</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z5" t="s">
         <v>35</v>
       </c>
-      <c r="V3" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3" t="s">
-        <v>51</v>
-      </c>
-      <c r="X3" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA3">
-        <v>13</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="3">
-        <v>39087</v>
-      </c>
-      <c r="D4" s="3">
-        <v>38807</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="3">
-        <v>39087</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="2">
-        <v>1</v>
-      </c>
-      <c r="N4" s="2">
-        <v>0</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA4" s="2">
-        <v>9</v>
-      </c>
-      <c r="AB4" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="3">
-        <v>39087</v>
-      </c>
-      <c r="D5" s="3">
-        <v>38807</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" s="3">
-        <v>39087</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="AA5">
+        <v>10</v>
+      </c>
+      <c r="AB5" t="s">
         <v>49</v>
-      </c>
-      <c r="K5" s="2">
-        <v>65101</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="2">
-        <v>1</v>
-      </c>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA5" s="2">
-        <v>13</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="3">
-        <v>39087</v>
-      </c>
-      <c r="D6" s="3">
-        <v>38807</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="3">
-        <v>39087</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="2">
-        <v>64400</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6" s="2">
-        <v>1</v>
-      </c>
-      <c r="N6" s="2">
-        <v>1</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="X6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AA6" s="2">
-        <v>50</v>
-      </c>
-      <c r="AB6" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="1">
-        <v>40007</v>
-      </c>
-      <c r="D7" s="1">
-        <v>39937</v>
-      </c>
-      <c r="E7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H7" s="1">
-        <v>40007</v>
-      </c>
-      <c r="I7" t="s">
-        <v>70</v>
-      </c>
-      <c r="J7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K7">
-        <v>63592</v>
-      </c>
-      <c r="L7" t="s">
-        <v>31</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>32</v>
-      </c>
-      <c r="P7" t="s">
-        <v>50</v>
-      </c>
-      <c r="S7" t="s">
-        <v>64</v>
-      </c>
-      <c r="T7" t="s">
-        <v>35</v>
-      </c>
-      <c r="U7" t="s">
-        <v>35</v>
-      </c>
-      <c r="V7" t="s">
-        <v>36</v>
-      </c>
-      <c r="W7" t="s">
-        <v>71</v>
-      </c>
-      <c r="X7" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA7">
-        <v>11</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="1">
-        <v>40023</v>
-      </c>
-      <c r="D8" s="1">
-        <v>39953</v>
-      </c>
-      <c r="E8" t="s">
-        <v>67</v>
-      </c>
-      <c r="H8" s="1">
-        <v>40023</v>
-      </c>
-      <c r="I8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8">
-        <v>6951</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>32</v>
-      </c>
-      <c r="P8" t="s">
-        <v>59</v>
-      </c>
-      <c r="S8" t="s">
-        <v>64</v>
-      </c>
-      <c r="T8" t="s">
-        <v>35</v>
-      </c>
-      <c r="U8" t="s">
-        <v>35</v>
-      </c>
-      <c r="V8" t="s">
-        <v>36</v>
-      </c>
-      <c r="W8" t="s">
-        <v>51</v>
-      </c>
-      <c r="X8" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA8">
-        <v>13</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="3">
-        <v>42740</v>
-      </c>
-      <c r="D9" s="3">
-        <v>42460</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="3">
-        <v>42740</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M9" s="2">
-        <v>1</v>
-      </c>
-      <c r="N9" s="2">
-        <v>0</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA9" s="2">
-        <v>9</v>
-      </c>
-      <c r="AB9" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="3">
-        <v>42740</v>
-      </c>
-      <c r="D10" s="3">
-        <v>42460</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H10" s="3">
-        <v>42740</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K10" s="2">
-        <v>65101</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M10" s="2">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2">
-        <v>0</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="X10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Z10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA10" s="2">
-        <v>13</v>
-      </c>
-      <c r="AB10" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="3">
-        <v>42740</v>
-      </c>
-      <c r="D11" s="3">
-        <v>42460</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" s="3">
-        <v>42740</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J11" t="s">
-        <v>69</v>
-      </c>
-      <c r="K11">
-        <v>63592</v>
-      </c>
-      <c r="L11" t="s">
-        <v>31</v>
-      </c>
-      <c r="M11" s="2">
-        <v>1</v>
-      </c>
-      <c r="N11" s="2">
-        <v>1</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W11" t="s">
-        <v>71</v>
-      </c>
-      <c r="X11" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y11"/>
-      <c r="Z11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA11">
-        <v>11</v>
-      </c>
-      <c r="AB11" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
